--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 50 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 48 clubs short</t>
         </is>
       </c>
     </row>
@@ -8204,13 +8204,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>5</v>
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8612,17 +8612,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M78" s="7" t="n">
@@ -8657,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8668,8 +8668,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" s="10" t="n">
         <v>1</v>
@@ -10733,7 +10733,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10803,8 +10803,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -13385,7 +13385,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13400,7 +13400,7 @@
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -13517,7 +13517,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3579,7 +3583,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4605,7 +4613,11 @@
       <c r="AB38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5009,7 +5021,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5518,7 +5534,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5720,7 +5740,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5922,7 +5946,11 @@
       <c r="AB51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -6948,7 +6976,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7962,7 +7994,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8782,7 +8818,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -8883,7 +8923,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9895,7 +9939,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10299,7 +10347,11 @@
       <c r="AB94" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -11329,7 +11381,11 @@
       <c r="AB104" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 48 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 45 clubs short</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1437,8 +1437,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29" s="9" t="n">
         <v>0</v>
@@ -4548,13 +4548,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -5469,13 +5469,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>4</v>
       </c>
       <c r="W47" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>7</v>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7379,8 +7379,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -8885,10 +8885,10 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10237,8 +10237,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -11504,11 +11504,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>7072</v>
+        <v>4486922</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Odessa Toastmasters Club</t>
+          <t>Dare To Master</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -11526,10 +11526,10 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11576,8 +11576,8 @@
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>0</v>
+      <c r="X106" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11589,7 +11589,7 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AC106" s="4" t="inlineStr"/>
     </row>
@@ -11605,11 +11605,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1509</v>
+        <v>7072</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Permian Toastmasters Club</t>
+          <t>Odessa Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11627,10 +11627,10 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K107" s="4" t="n">
         <v>0</v>
@@ -11663,7 +11663,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T107" s="10" t="n">
         <v>1</v>
@@ -11677,8 +11677,8 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="10" t="n">
-        <v>5</v>
+      <c r="X107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11690,13 +11690,9 @@
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11710,15 +11706,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>3165</v>
+        <v>1509</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Pop-Up Toastmasters Club</t>
+          <t>Permian Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11759,7 +11755,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11768,10 +11764,10 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
@@ -11783,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11797,7 +11793,11 @@
       <c r="AB108" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11811,15 +11811,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>4486922</v>
+        <v>3165</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>San Angelo Toastmasters</t>
+          <t>Pop-Up Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
@@ -11871,8 +11871,8 @@
       <c r="S109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T109" s="10" t="n">
-        <v>1</v>
+      <c r="T109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13375,7 +13375,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13540,7 +13540,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 45 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -831,24 +831,24 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>28678584</v>
+        <v>6191</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>MRLP ToastMaster</t>
+          <t>Afterburners Club</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q2" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S2" s="9" t="n">
         <v>0</v>
@@ -906,26 +906,32 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>0</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X2" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AB2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -939,15 +945,15 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>6191</v>
+        <v>7975857</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Afterburners Club</t>
+          <t>Blue Castle Collaborators</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -961,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -988,16 +994,16 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="9" t="n">
         <v>0</v>
@@ -1005,8 +1011,8 @@
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="10" t="n">
-        <v>4</v>
+      <c r="V3" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1024,11 +1030,11 @@
         <v>1</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -1044,11 +1050,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>7975857</v>
+        <v>3178</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Blue Castle Collaborators</t>
+          <t>Longhorn Toastmasters Club</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -1066,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1096,13 +1102,13 @@
         <v>0</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="9" t="n">
         <v>0</v>
@@ -1111,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1129,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1149,11 +1155,11 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3178</v>
+        <v>1826942</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Longhorn Toastmasters Club</t>
+          <t>Tarrant County Toastmasters</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -1171,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>21</v>
-      </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1201,13 +1207,13 @@
         <v>0</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="9" t="n">
         <v>0</v>
@@ -1216,13 +1222,13 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X5" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1234,11 +1240,11 @@
         <v>1</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -1250,15 +1256,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1826942</v>
+        <v>3626237</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Tarrant County Toastmasters</t>
+          <t>Jacobs - Fort Worth</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -1276,17 +1282,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="7" t="n">
@@ -1312,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="9" t="n">
         <v>0</v>
@@ -1321,31 +1327,27 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1359,11 +1361,11 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3626237</v>
+        <v>349</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Jacobs - Fort Worth</t>
+          <t>Plus-Two Toastmasters</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -1381,17 +1383,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M7" s="7" t="n">
@@ -1432,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -1444,9 +1446,13 @@
         <v>1</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1460,11 +1466,11 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>349</v>
+        <v>28678878</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Plus-Two Toastmasters</t>
+          <t>Speak Brilliantly</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -1482,10 +1488,10 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
@@ -1545,13 +1551,9 @@
         <v>1</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1565,15 +1567,15 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>28678878</v>
+        <v>9595</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Speak Brilliantly</t>
+          <t>Tip Top Toastmasters</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1587,17 +1589,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
@@ -1614,7 +1616,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>0</v>
@@ -1632,25 +1634,25 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="4" t="inlineStr"/>
     </row>
@@ -1662,19 +1664,19 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9595</v>
+        <v>706449</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Tip Top Toastmasters</t>
+          <t>Burleson Toastmasters Club</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1688,17 +1690,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M10" s="7" t="n">
@@ -1723,11 +1725,11 @@
       <c r="R10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="S10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -1751,9 +1753,13 @@
         <v>1</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1767,15 +1773,15 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>706449</v>
+        <v>5496</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Burleson Toastmasters Club</t>
+          <t>Cowtown Toastmasters</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1789,17 +1795,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
@@ -1816,7 +1822,7 @@
         </is>
       </c>
       <c r="P11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>0</v>
@@ -1824,8 +1830,8 @@
       <c r="R11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="10" t="n">
-        <v>2</v>
+      <c r="S11" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T11" s="10" t="n">
         <v>1</v>
@@ -1834,31 +1840,27 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="10" t="n">
-        <v>1</v>
+      <c r="Z11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AC11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1872,15 +1874,15 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5496</v>
+        <v>8474</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Cowtown Toastmasters</t>
+          <t>First Command Club</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1894,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1930,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" s="10" t="n">
         <v>1</v>
@@ -1938,26 +1940,26 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>0</v>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC12" s="4" t="inlineStr"/>
     </row>
@@ -1973,15 +1975,15 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8474</v>
+        <v>6480015</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>First Command Club</t>
+          <t>Motor Mouths</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1995,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2022,7 +2024,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -2031,16 +2033,16 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="10" t="n">
-        <v>4</v>
+      <c r="V13" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2058,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC13" s="4" t="inlineStr"/>
     </row>
@@ -2074,15 +2076,15 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6480015</v>
+        <v>897575</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Motor Mouths</t>
+          <t>Out On The Town</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2096,17 +2098,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2123,7 +2125,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2141,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2152,16 +2154,20 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC14" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2171,15 +2177,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>897575</v>
+        <v>638381</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Out On The Town</t>
+          <t>Centex Clearly Speaking Toastmasters</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -2197,17 +2203,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2242,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2260,13 +2266,9 @@
         <v>1</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2280,15 +2282,15 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>638381</v>
+        <v>7351</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Centex Clearly Speaking Toastmasters</t>
+          <t>Fish Pond Club</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2302,17 +2304,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M16" s="7" t="n">
@@ -2347,25 +2349,25 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X16" s="10" t="n">
-        <v>5</v>
+      <c r="X16" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="4" t="inlineStr"/>
     </row>
@@ -2381,15 +2383,15 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>7351</v>
+        <v>676842</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Fish Pond Club</t>
+          <t>Heart of Texas Bridge Gappers Club</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2403,17 +2405,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
@@ -2433,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
@@ -2441,8 +2443,8 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2453,20 +2455,20 @@
       <c r="W17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>1</v>
+      <c r="X17" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC17" s="4" t="inlineStr"/>
     </row>
@@ -2482,11 +2484,11 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>676842</v>
+        <v>3546</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Heart of Texas Bridge Gappers Club</t>
+          <t>Waco - Early Birds Club</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -2504,13 +2506,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2531,10 +2533,10 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2549,13 +2551,13 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -2567,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC18" s="4" t="inlineStr"/>
     </row>
@@ -2583,11 +2585,11 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3546</v>
+        <v>5529749</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Waco - Early Birds Club</t>
+          <t>Warriors With Words</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
@@ -2605,13 +2607,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2632,7 +2634,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2650,13 +2652,13 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -2668,27 +2670,27 @@
         <v>1</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>5529749</v>
+        <v>1582921</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Warriors With Words</t>
+          <t>Colleyville Toastmasters</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -2706,13 +2708,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2733,7 +2735,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2744,32 +2746,32 @@
       <c r="S20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T20" s="10" t="n">
-        <v>1</v>
+      <c r="T20" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
     </row>
@@ -2785,11 +2787,11 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1582921</v>
+        <v>1912</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Colleyville Toastmasters</t>
+          <t>Grace Club</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -2810,10 +2812,10 @@
         <v>14</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2852,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
@@ -2870,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
     </row>
@@ -2886,11 +2888,11 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1912</v>
+        <v>7663722</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Grace Club</t>
+          <t>Mindful Masters</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2908,10 +2910,10 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0</v>
@@ -2958,8 +2960,8 @@
       <c r="W22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="10" t="n">
-        <v>4</v>
+      <c r="X22" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -2971,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC22" s="4" t="inlineStr"/>
     </row>
@@ -2987,15 +2989,15 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7663722</v>
+        <v>7974117</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Mindful Masters</t>
+          <t>Professional Speakers Support Group Advanced</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3009,13 +3011,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3036,7 +3038,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -3045,36 +3047,40 @@
         <v>0</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X23" s="9" t="n">
-        <v>2</v>
+      <c r="X23" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3088,15 +3094,15 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>7974117</v>
+        <v>28679483</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Professional Speakers Support Group Advanced</t>
+          <t>Toastmasters of Central Cencora</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3110,17 +3116,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M24" s="7" t="n">
@@ -3137,7 +3143,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3146,40 +3152,36 @@
         <v>0</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="10" t="n">
-        <v>1</v>
+      <c r="Z24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC24" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3189,19 +3191,19 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>28679483</v>
+        <v>3692</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of Central Cencora</t>
+          <t>Lakeside TAC Leaders</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3215,17 +3217,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="7" t="n">
@@ -3251,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="9" t="n">
         <v>0</v>
@@ -3260,25 +3262,25 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X25" s="9" t="n">
-        <v>2</v>
+      <c r="X25" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC25" s="4" t="inlineStr"/>
     </row>
@@ -3294,15 +3296,15 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3692</v>
+        <v>7850107</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Lakeside TAC Leaders</t>
+          <t>Lewisville Area Toastmasters Club</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3316,17 +3318,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J26" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M26" s="7" t="n">
@@ -3360,26 +3362,26 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" s="9" t="n">
-        <v>0</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X26" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC26" s="4" t="inlineStr"/>
     </row>
@@ -3395,15 +3397,15 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7850107</v>
+        <v>3467810</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Lewisville Area Toastmasters Club</t>
+          <t>Progressive Leaders</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3417,13 +3419,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3444,10 +3446,10 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3455,34 +3457,38 @@
       <c r="S27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W27" s="10" t="n">
-        <v>4</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3496,15 +3502,15 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3467810</v>
+        <v>7594460</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Progressive Leaders</t>
+          <t>Taste of Toastmasters</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3518,17 +3524,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="7" t="n">
@@ -3545,7 +3551,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3554,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="S28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3581,11 +3587,11 @@
         <v>1</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -3601,15 +3607,15 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7594460</v>
+        <v>2219278</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Taste of Toastmasters</t>
+          <t>WBC Toastmasters</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3623,10 +3629,10 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" s="4" t="n">
         <v>13</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>2</v>
@@ -3650,19 +3656,19 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>0</v>
+      <c r="S29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U29" s="9" t="n">
         <v>0</v>
@@ -3686,13 +3692,9 @@
         <v>1</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3702,19 +3704,19 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2219278</v>
+        <v>1476720</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>WBC Toastmasters</t>
+          <t>Flower Mound Toastmasters</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3728,17 +3730,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M30" s="7" t="n">
@@ -3758,28 +3760,28 @@
         <v>1</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="10" t="n">
-        <v>2</v>
+      <c r="S30" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W30" s="9" t="n">
-        <v>0</v>
+      <c r="U30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W30" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X30" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -3791,9 +3793,13 @@
         <v>1</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3807,15 +3813,15 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1476720</v>
+        <v>5297</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Flower Mound Toastmasters</t>
+          <t>Golden Triangle Toastmasters Club</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3829,17 +3835,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
@@ -3858,8 +3864,8 @@
       <c r="P31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="9" t="n">
-        <v>0</v>
+      <c r="Q31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>0</v>
@@ -3870,17 +3876,17 @@
       <c r="T31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W31" s="10" t="n">
+      <c r="U31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="X31" s="10" t="n">
-        <v>6</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -3894,11 +3900,7 @@
       <c r="AB31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC31" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -3912,15 +3914,15 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5297</v>
+        <v>28676009</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Golden Triangle Toastmasters Club</t>
+          <t>Lantana Toastmasters</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3934,13 +3936,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -3961,43 +3963,43 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="10" t="n">
-        <v>5</v>
+      <c r="X32" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="10" t="n">
-        <v>1</v>
+      <c r="Z32" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC32" s="4" t="inlineStr"/>
     </row>
@@ -4013,15 +4015,15 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>28676009</v>
+        <v>6792146</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Lantana Toastmasters</t>
+          <t>Microsoft Toasters 365</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4035,17 +4037,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
@@ -4080,27 +4082,31 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4114,15 +4120,15 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6792146</v>
+        <v>6619708</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Microsoft Toasters 365</t>
+          <t>Smiling Stars</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4136,13 +4142,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4163,7 +4169,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>0</v>
@@ -4172,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -4181,29 +4187,29 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X34" s="9" t="n">
-        <v>3</v>
+      <c r="X34" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -4215,15 +4221,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6619708</v>
+        <v>6103644</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Smiling Stars</t>
+          <t>Bookmasters</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
@@ -4241,17 +4247,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
@@ -4268,7 +4274,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4277,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" s="9" t="n">
         <v>0</v>
@@ -4286,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4304,13 +4310,9 @@
         <v>1</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC35" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4324,11 +4326,11 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>6103644</v>
+        <v>28679366</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Bookmasters</t>
+          <t>Catalyst Communicators</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -4346,17 +4348,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M36" s="7" t="n">
@@ -4391,13 +4393,13 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X36" s="10" t="n">
-        <v>7</v>
+      <c r="X36" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y36" s="9" t="n">
         <v>0</v>
@@ -4409,7 +4411,7 @@
         <v>1</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC36" s="4" t="inlineStr"/>
     </row>
@@ -4425,15 +4427,15 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>28679366</v>
+        <v>1540842</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Catalyst Communicators</t>
+          <t>Circle of Excellence</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4447,10 +4449,10 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>2</v>
@@ -4474,22 +4476,22 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V37" s="9" t="n">
         <v>2</v>
@@ -4497,8 +4499,8 @@
       <c r="W37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="9" t="n">
-        <v>3</v>
+      <c r="X37" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y37" s="9" t="n">
         <v>0</v>
@@ -4510,9 +4512,13 @@
         <v>1</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC37" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC37" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4526,116 +4532,112 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1540842</v>
+        <v>7518138</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Circle of Excellence</t>
+          <t>DTCC - Dallas Toastmasters</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O38" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC38" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7518138</v>
+        <v>28675570</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>DTCC - Dallas Toastmasters</t>
+          <t>Dragos Toastmasters</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
@@ -4653,17 +4655,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="7" t="n">
@@ -4709,14 +4711,14 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="10" t="n">
-        <v>1</v>
+      <c r="Z39" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC39" s="4" t="inlineStr"/>
     </row>
@@ -4732,11 +4734,11 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>28675570</v>
+        <v>1378170</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Dragos Toastmasters</t>
+          <t>Fort Worth Project Management Toastmasters</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -4754,10 +4756,10 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>0</v>
@@ -4768,11 +4770,11 @@
         </is>
       </c>
       <c r="M40" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O40" s="8" t="inlineStr">
@@ -4805,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y40" s="9" t="n">
         <v>0</v>
@@ -4813,11 +4815,11 @@
       <c r="Z40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA40" s="9" t="n">
-        <v>0</v>
+      <c r="AA40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC40" s="4" t="inlineStr"/>
     </row>
@@ -4833,15 +4835,15 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1378170</v>
+        <v>3332446</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Fort Worth Project Management Toastmasters</t>
+          <t>Highway To Excellence</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4855,17 +4857,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
@@ -4891,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="9" t="n">
         <v>0</v>
@@ -4900,27 +4902,31 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X41" s="9" t="n">
-        <v>3</v>
+      <c r="X41" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4934,11 +4940,11 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>3332446</v>
+        <v>7694</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Highway To Excellence</t>
+          <t>MidCities Achievers</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -4956,17 +4962,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="7" t="n">
@@ -4986,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -5001,31 +5007,27 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X42" s="10" t="n">
+      <c r="X42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC42" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5039,15 +5041,15 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>7694</v>
+        <v>7744858</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>MidCities Achievers</t>
+          <t>NST Toastmasters Club</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5061,17 +5063,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
@@ -5091,28 +5093,28 @@
         <v>0</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="9" t="n">
-        <v>0</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X43" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
@@ -5136,19 +5138,19 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>7744858</v>
+        <v>2474402</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>NST Toastmasters Club</t>
+          <t>ARBOR Toastmasters</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5162,17 +5164,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="7" t="n">
@@ -5189,7 +5191,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5204,16 +5206,16 @@
         <v>1</v>
       </c>
       <c r="U44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V44" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W44" s="10" t="n">
-        <v>4</v>
+      <c r="W44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X44" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
@@ -5225,9 +5227,13 @@
         <v>1</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5241,15 +5247,15 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2474402</v>
+        <v>7173767</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>ARBOR Toastmasters</t>
+          <t>Grand Orators</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5263,13 +5269,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5277,11 +5283,11 @@
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O45" s="8" t="inlineStr">
@@ -5304,17 +5310,17 @@
       <c r="T45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U45" s="10" t="n">
-        <v>1</v>
+      <c r="U45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X45" s="10" t="n">
-        <v>7</v>
+      <c r="X45" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y45" s="9" t="n">
         <v>0</v>
@@ -5322,17 +5328,13 @@
       <c r="Z45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA45" s="10" t="n">
-        <v>1</v>
+      <c r="AA45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC45" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5346,15 +5348,15 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>7173767</v>
+        <v>28678015</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Grand Orators</t>
+          <t>Mansfield Toastmasters</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5368,25 +5370,25 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>10</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -5395,7 +5397,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5409,31 +5411,35 @@
       <c r="T46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="9" t="n">
-        <v>3</v>
+      <c r="U46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W46" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X46" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5447,15 +5453,15 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>28678015</v>
+        <v>3017469</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Mansfield Toastmasters</t>
+          <t>NCTCOG Toastmasters</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5469,17 +5475,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
@@ -5496,7 +5502,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5507,17 +5513,17 @@
       <c r="S47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T47" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W47" s="10" t="n">
-        <v>6</v>
+      <c r="T47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>7</v>
@@ -5525,20 +5531,16 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="10" t="n">
-        <v>1</v>
+      <c r="Z47" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC47" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5552,15 +5554,15 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>3017469</v>
+        <v>593906</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>NCTCOG Toastmasters</t>
+          <t>Skymasters Club</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5574,17 +5576,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M48" s="7" t="n">
@@ -5619,27 +5621,31 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X48" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5649,15 +5655,15 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>593906</v>
+        <v>3214758</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Skymasters Club</t>
+          <t>ACH Renaissance</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -5675,17 +5681,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
@@ -5702,7 +5708,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -5711,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="9" t="n">
         <v>0</v>
@@ -5720,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X49" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y49" s="9" t="n">
         <v>0</v>
@@ -5738,13 +5744,9 @@
         <v>1</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC49" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5758,15 +5760,15 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>3214758</v>
+        <v>7514</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>ACH Renaissance</t>
+          <t>Arlington Nooners Toastmasters Club</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5780,17 +5782,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
@@ -5807,10 +5809,10 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
@@ -5825,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5843,9 +5845,13 @@
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5859,15 +5865,15 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>7514</v>
+        <v>7742649</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Arlington Nooners Toastmasters Club</t>
+          <t>CAE USA Toastmasters</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5881,17 +5887,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
@@ -5908,16 +5914,16 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q51" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" s="9" t="n">
         <v>0</v>
@@ -5944,11 +5950,11 @@
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC51" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -5964,15 +5970,15 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>7742649</v>
+        <v>4538</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>CAE USA Toastmasters</t>
+          <t>Power Communicators Toastmasters Club</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5986,13 +5992,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -6013,10 +6019,10 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6031,31 +6037,27 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X52" s="10" t="n">
-        <v>7</v>
+      <c r="X52" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6065,15 +6067,15 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>4538</v>
+        <v>28678057</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Power Communicators Toastmasters Club</t>
+          <t>Bell Toastmasters</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -6091,10 +6093,10 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>0</v>
@@ -6105,11 +6107,11 @@
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O53" s="8" t="inlineStr">
@@ -6118,10 +6120,10 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6142,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="X53" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
@@ -6150,11 +6152,11 @@
       <c r="Z53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA53" s="10" t="n">
-        <v>1</v>
+      <c r="AA53" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="4" t="inlineStr"/>
     </row>
@@ -6170,11 +6172,11 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>28678057</v>
+        <v>4370</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Bell Toastmasters</t>
+          <t>Flagship Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
@@ -6192,13 +6194,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6206,11 +6208,11 @@
         </is>
       </c>
       <c r="M54" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O54" s="8" t="inlineStr">
@@ -6237,13 +6239,13 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X54" s="9" t="n">
-        <v>0</v>
+      <c r="X54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
@@ -6251,11 +6253,11 @@
       <c r="Z54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA54" s="9" t="n">
-        <v>0</v>
+      <c r="AA54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC54" s="4" t="inlineStr"/>
     </row>
@@ -6271,15 +6273,15 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>4370</v>
+        <v>7407</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Flagship Speakers Toastmasters Club</t>
+          <t>Pro A.M. Toastmasters Club</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6296,10 +6298,10 @@
         <v>15</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -6323,42 +6325,46 @@
         <v>0</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X55" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC55" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6372,11 +6378,11 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>7407</v>
+        <v>6530</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Pro A.M. Toastmasters Club</t>
+          <t>United Communicators Toastmasters</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
@@ -6394,17 +6400,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M56" s="7" t="n">
@@ -6424,13 +6430,13 @@
         <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" s="10" t="n">
         <v>1</v>
@@ -6439,13 +6445,13 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X56" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6457,11 +6463,11 @@
         <v>1</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -6477,11 +6483,11 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>6530</v>
+        <v>6332</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>United Communicators Toastmasters</t>
+          <t>World Renowned Grand Prairie Toastmasters Club</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -6499,13 +6505,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6535,22 +6541,22 @@
         <v>0</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T57" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>3</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X57" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6573,24 +6579,24 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>6332</v>
+        <v>6655730</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>World Renowned Grand Prairie Toastmasters Club</t>
+          <t>FHLB Dallas Toastmasters</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6604,17 +6610,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="7" t="n">
@@ -6640,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" s="9" t="n">
         <v>0</v>
@@ -6648,32 +6654,28 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="10" t="n">
-        <v>4</v>
+      <c r="V58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X58" s="10" t="n">
-        <v>7</v>
+      <c r="X58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="10" t="n">
-        <v>1</v>
+      <c r="Z58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC58" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6687,15 +6689,15 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>6655730</v>
+        <v>1879279</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>FHLB Dallas Toastmasters</t>
+          <t>Golden Toasties</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6709,13 +6711,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6745,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -6754,25 +6756,25 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>0</v>
+      <c r="X59" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC59" s="4" t="inlineStr"/>
     </row>
@@ -6788,15 +6790,15 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1879279</v>
+        <v>3365</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Golden Toasties</t>
+          <t>Irving Toastmasters Club</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6810,17 +6812,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M60" s="7" t="n">
@@ -6837,16 +6839,16 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" s="9" t="n">
         <v>0</v>
@@ -6855,7 +6857,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6873,9 +6875,13 @@
         <v>1</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6889,15 +6895,15 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>3365</v>
+        <v>4354</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Irving Toastmasters Club</t>
+          <t>Off The Cuff</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6911,13 +6917,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6938,25 +6944,25 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="9" t="n">
-        <v>0</v>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6974,11 +6980,11 @@
         <v>1</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC61" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -6994,15 +7000,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>4354</v>
+        <v>629</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Off The Cuff</t>
+          <t>Six Twenty Nine Club</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7016,17 +7022,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
@@ -7054,38 +7060,34 @@
       <c r="S62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" s="10" t="n">
-        <v>1</v>
+      <c r="T62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X62" s="10" t="n">
-        <v>7</v>
+      <c r="X62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="10" t="n">
-        <v>1</v>
+      <c r="Z62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC62" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7099,11 +7101,11 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>629</v>
+        <v>4567</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Six Twenty Nine Club</t>
+          <t>Vizient Toastmasters</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -7121,13 +7123,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -7135,11 +7137,11 @@
         </is>
       </c>
       <c r="M63" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O63" s="8" t="inlineStr">
@@ -7166,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7180,11 +7182,11 @@
       <c r="Z63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA63" s="10" t="n">
-        <v>1</v>
+      <c r="AA63" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC63" s="4" t="inlineStr"/>
     </row>
@@ -7196,19 +7198,19 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>4567</v>
+        <v>28680086</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Vizient Toastmasters</t>
+          <t>Fluor Corporate HQ Toastmasters</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7222,25 +7224,25 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O64" s="8" t="inlineStr">
@@ -7267,22 +7269,22 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X64" s="9" t="n">
-        <v>0</v>
+      <c r="X64" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
         <v>1</v>
@@ -7301,15 +7303,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>28680086</v>
+        <v>3349691</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Fluor Corporate HQ Toastmasters</t>
+          <t>Launchpad Speakers</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7323,25 +7325,25 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O65" s="8" t="inlineStr">
@@ -7368,25 +7370,25 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X65" s="10" t="n">
-        <v>6</v>
+      <c r="X65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="10" t="n">
-        <v>1</v>
+      <c r="Z65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC65" s="4" t="inlineStr"/>
     </row>
@@ -7402,15 +7404,15 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>3349691</v>
+        <v>5922</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Launchpad Speakers</t>
+          <t>Nissan Toastmasters Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7424,10 +7426,10 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>0</v>
@@ -7438,11 +7440,11 @@
         </is>
       </c>
       <c r="M66" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O66" s="8" t="inlineStr">
@@ -7451,7 +7453,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7460,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="9" t="n">
         <v>0</v>
@@ -7474,20 +7476,20 @@
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X66" s="9" t="n">
-        <v>0</v>
+      <c r="X66" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC66" s="4" t="inlineStr"/>
     </row>
@@ -7503,15 +7505,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>5922</v>
+        <v>7502</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Nissan Toastmasters Club</t>
+          <t>Successful Speakers Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7525,17 +7527,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M67" s="7" t="n">
@@ -7552,7 +7554,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7581,8 +7583,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="10" t="n">
-        <v>1</v>
+      <c r="Z67" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7604,15 +7606,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>7502</v>
+        <v>2517471</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Successful Speakers Club</t>
+          <t>Top Flight Toastmasters Club</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7626,17 +7628,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="7" t="n">
@@ -7662,7 +7664,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -7676,20 +7678,20 @@
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="10" t="n">
-        <v>6</v>
+      <c r="X68" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC68" s="4" t="inlineStr"/>
     </row>
@@ -7701,15 +7703,15 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>2517471</v>
+        <v>28677380</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Top Flight Toastmasters Club</t>
+          <t>Core Conversations</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -7727,10 +7729,10 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>0</v>
@@ -7741,11 +7743,11 @@
         </is>
       </c>
       <c r="M69" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O69" s="8" t="inlineStr">
@@ -7778,19 +7780,19 @@
         <v>0</v>
       </c>
       <c r="X69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="10" t="n">
-        <v>1</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA69" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB69" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC69" s="4" t="inlineStr"/>
     </row>
@@ -7806,15 +7808,15 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>28677380</v>
+        <v>1483991</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Core Conversations</t>
+          <t>IT Leaders and Speakers of Tomorrow Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7828,25 +7830,25 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M70" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O70" s="8" t="inlineStr">
@@ -7855,7 +7857,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -7866,20 +7868,20 @@
       <c r="S70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>0</v>
+      <c r="V70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="X70" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7887,13 +7889,17 @@
       <c r="Z70" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA70" s="9" t="n">
-        <v>0</v>
+      <c r="AA70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7907,15 +7913,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1483991</v>
+        <v>3331520</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>IT Leaders and Speakers of Tomorrow Toastmasters Club</t>
+          <t>Strategic Communicators</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7929,17 +7935,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="7" t="n">
@@ -7959,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="9" t="n">
         <v>0</v>
@@ -7967,17 +7973,17 @@
       <c r="S71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T71" s="10" t="n">
-        <v>1</v>
+      <c r="T71" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="10" t="n">
-        <v>4</v>
+      <c r="V71" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -7992,11 +7998,11 @@
         <v>1</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC71" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -8012,15 +8018,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>3331520</v>
+        <v>4396433</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Strategic Communicators</t>
+          <t>The PIE Effect</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8034,13 +8040,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -8061,7 +8067,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>1</v>
@@ -8070,16 +8076,16 @@
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8090,20 +8096,16 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="10" t="n">
-        <v>1</v>
+      <c r="Z72" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC72" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8113,19 +8115,19 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>4396433</v>
+        <v>2194281</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>The PIE Effect</t>
+          <t>Electric Toasters</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8139,17 +8141,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="7" t="n">
@@ -8166,16 +8168,16 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="9" t="n">
-        <v>1</v>
+      <c r="S73" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T73" s="10" t="n">
         <v>1</v>
@@ -8183,28 +8185,32 @@
       <c r="U73" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>1</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8218,15 +8224,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2194281</v>
+        <v>28678846</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Electric Toasters</t>
+          <t>Hidden Ridge Communicators</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8240,25 +8246,25 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L74" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O74" s="8" t="inlineStr">
@@ -8270,46 +8276,42 @@
         <v>0</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S74" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T74" s="10" t="n">
-        <v>1</v>
+      <c r="S74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="10" t="n">
-        <v>4</v>
+      <c r="V74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X74" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA74" s="10" t="n">
-        <v>1</v>
+      <c r="Z74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC74" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8323,15 +8325,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>28678846</v>
+        <v>5265032</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Hidden Ridge Communicators</t>
+          <t>Las Colinas Professionals</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8345,13 +8347,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8359,11 +8361,11 @@
         </is>
       </c>
       <c r="M75" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O75" s="8" t="inlineStr">
@@ -8375,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8389,26 +8391,26 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="9" t="n">
-        <v>0</v>
+      <c r="V75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="9" t="n">
-        <v>2</v>
+      <c r="X75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC75" s="4" t="inlineStr"/>
     </row>
@@ -8424,15 +8426,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>5265032</v>
+        <v>5966167</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Las Colinas Professionals</t>
+          <t>MLCC Toastmasters</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8446,70 +8448,70 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="L76" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N76" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O76" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB76" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="AC76" s="4" t="inlineStr"/>
     </row>
@@ -8525,11 +8527,11 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>5966167</v>
+        <v>28678584</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>MLCC Toastmasters</t>
+          <t>MRLP ToastMaster</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -8547,25 +8549,25 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K77" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M77" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O77" s="8" t="inlineStr">
@@ -8598,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8606,12 +8608,10 @@
       <c r="Z77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="AA77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB77" s="4" t="n"/>
       <c r="AC77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9120,8 +9120,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9221,8 +9221,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9322,8 +9322,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9405,8 +9405,8 @@
       <c r="S85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10035,8 +10035,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10130,14 +10130,14 @@
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>3</v>
+      <c r="X92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10309,7 +10309,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -10323,8 +10323,8 @@
       <c r="T94" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
+      <c r="U94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V94" s="10" t="n">
         <v>4</v>
@@ -10417,7 +10417,7 @@
         <v>0</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10548,8 +10548,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10940,7 +10940,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="9" t="n">
         <v>0</v>
@@ -11160,8 +11160,8 @@
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>3</v>
+      <c r="X102" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11970,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" s="10" t="n">
         <v>1</v>
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>1</v>
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12305,8 +12305,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12744,7 +12744,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12814,8 +12814,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12837,7 +12837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12901,25 +12901,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -12928,7 +12928,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -12939,14 +12939,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -12961,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -12972,20 +12972,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -13005,7 +13005,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -13027,18 +13027,18 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -13071,14 +13071,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13093,7 +13093,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -13104,20 +13104,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -13126,7 +13126,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -13137,17 +13137,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -13156,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -13165,22 +13165,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -13192,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -13203,14 +13203,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -13255,10 +13255,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -13269,53 +13269,53 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -13335,20 +13335,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -13368,20 +13368,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -13401,59 +13401,59 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
@@ -13467,20 +13467,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -13500,17 +13500,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>2</v>
@@ -13533,14 +13533,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13555,25 +13555,25 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13588,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -13599,20 +13599,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -13621,7 +13621,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -13632,20 +13632,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -13654,7 +13654,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -13665,20 +13665,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -13687,44 +13687,11 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -900,8 +900,8 @@
       <c r="S2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="9" t="n">
-        <v>0</v>
+      <c r="T2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="9" t="n">
         <v>0</v>
@@ -967,17 +967,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="7" t="n">
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1072,17 +1072,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1177,17 +1177,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1383,17 +1383,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="7" t="n">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1532,11 +1532,11 @@
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="9" t="n">
-        <v>0</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>6</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1690,17 +1690,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="7" t="n">
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2098,17 +2098,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>1</v>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="10" t="n">
         <v>1</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2651,11 +2651,11 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>2</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>4</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -3116,17 +3116,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="7" t="n">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3318,17 +3318,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="7" t="n">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3445,8 +3445,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P27" s="9" t="n">
-        <v>3</v>
+      <c r="P27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>1</v>
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="9" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3658,14 +3658,14 @@
       <c r="P29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" s="9" t="n">
-        <v>1</v>
+      <c r="Q29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S29" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" s="10" t="n">
         <v>1</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -4037,17 +4037,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
@@ -4142,17 +4142,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="7" t="n">
@@ -4247,13 +4247,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4348,17 +4348,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="7" t="n">
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4449,13 +4449,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4756,13 +4756,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4962,13 +4962,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -5006,11 +5006,11 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>2</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="9" t="n">
         <v>0</v>
@@ -5063,17 +5063,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
@@ -5111,7 +5111,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>5</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5370,13 +5370,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>10</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>2</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5576,17 +5576,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="7" t="n">
@@ -5614,14 +5614,14 @@
       <c r="S48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="9" t="n">
-        <v>0</v>
+      <c r="T48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5782,17 +5782,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5931,8 +5931,8 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>1</v>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -6093,13 +6093,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6194,13 +6194,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -6400,17 +6400,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="7" t="n">
@@ -6505,17 +6505,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="7" t="n">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6749,8 +6749,8 @@
       <c r="S59" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T59" s="9" t="n">
-        <v>0</v>
+      <c r="T59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U59" s="9" t="n">
         <v>0</v>
@@ -6812,13 +6812,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6917,17 +6917,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="7" t="n">
@@ -7022,13 +7022,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -7123,13 +7123,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -7224,13 +7224,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7325,13 +7325,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7426,13 +7426,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7583,8 +7583,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7628,13 +7628,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7729,13 +7729,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7830,13 +7830,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
@@ -8040,13 +8040,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -8141,13 +8141,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8246,13 +8246,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8347,13 +8347,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8448,13 +8448,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8605,8 +8605,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8648,17 +8648,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="7" t="n">
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8753,17 +8753,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="7" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8963,13 +8963,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9064,13 +9064,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -9108,11 +9108,11 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>0</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" s="9" t="n">
         <v>2</v>
@@ -9165,13 +9165,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9367,17 +9367,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="7" t="n">
@@ -9412,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9571,13 +9571,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9672,13 +9672,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9773,13 +9773,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
@@ -9874,13 +9874,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>7</v>
@@ -9979,13 +9979,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -10080,13 +10080,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10181,13 +10181,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -10225,8 +10225,8 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>1</v>
+      <c r="V93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10282,13 +10282,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10387,17 +10387,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -10492,13 +10492,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10593,13 +10593,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10694,17 +10694,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L98" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="7" t="n">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10799,17 +10799,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="7" t="n">
@@ -10843,8 +10843,8 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>2</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10904,17 +10904,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="7" t="n">
@@ -10939,8 +10939,8 @@
       <c r="R100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="9" t="n">
-        <v>1</v>
+      <c r="S100" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T100" s="9" t="n">
         <v>0</v>
@@ -11009,13 +11009,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
@@ -11110,13 +11110,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11316,13 +11316,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11421,17 +11421,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L105" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="7" t="n">
@@ -11526,13 +11526,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11627,13 +11627,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11728,13 +11728,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11934,13 +11934,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -11975,8 +11975,8 @@
       <c r="T110" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U110" s="9" t="n">
-        <v>0</v>
+      <c r="U110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V110" s="9" t="n">
         <v>1</v>
@@ -12039,17 +12039,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L111" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="7" t="n">
@@ -12144,13 +12144,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -12249,13 +12249,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
@@ -12350,13 +12350,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -12451,13 +12451,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>2</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12552,13 +12552,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12657,13 +12657,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12913,13 +12913,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -12928,7 +12928,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -12946,7 +12946,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -12961,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -12994,7 +12994,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13012,7 +13012,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13060,7 +13060,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13078,7 +13078,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13093,7 +13093,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -13126,7 +13126,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13177,7 +13177,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -13192,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -13210,7 +13210,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -13243,7 +13243,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13258,7 +13258,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13291,7 +13291,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13309,7 +13309,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13324,7 +13324,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -13342,7 +13342,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13408,7 +13408,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -13423,7 +13423,7 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13441,7 +13441,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13456,7 +13456,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -13489,7 +13489,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -13507,7 +13507,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13522,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -13540,7 +13540,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -13588,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -13639,7 +13639,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13654,7 +13654,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X2" s="10" t="n">
         <v>7</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1005,8 +1005,8 @@
       <c r="S3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="9" t="n">
-        <v>0</v>
+      <c r="T3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1383,13 +1383,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2547,8 +2547,8 @@
       <c r="T18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U18" s="9" t="n">
-        <v>0</v>
+      <c r="U18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>0</v>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>4</v>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3673,8 +3673,8 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>3</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -8448,13 +8448,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8753,13 +8753,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" s="9" t="n">
         <v>0</v>
@@ -9874,13 +9874,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>7</v>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" s="10" t="n">
         <v>1</v>
@@ -10799,13 +10799,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L100" s="8" t="inlineStr">
         <is>
@@ -11110,13 +11110,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -11316,13 +11316,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11934,13 +11934,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" s="9" t="n">
         <v>0</v>
@@ -12913,7 +12913,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -13012,7 +13012,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13078,13 +13078,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/docs/d/25/inyear.xlsx
+++ b/docs/d/25/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1937,8 +1937,8 @@
       <c r="T12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
+      <c r="U12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
         <v>4</v>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3448,8 +3448,8 @@
       <c r="P27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>1</v>
+      <c r="Q27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3562,8 +3562,8 @@
       <c r="S28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T28" s="9" t="n">
-        <v>0</v>
+      <c r="T28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U28" s="9" t="n">
         <v>0</v>
@@ -4247,13 +4247,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4449,13 +4449,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4886,8 +4886,8 @@
       <c r="P41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="9" t="n">
-        <v>1</v>
+      <c r="Q41" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>0</v>
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>1</v>
       </c>
       <c r="S60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="9" t="n">
         <v>0</v>
@@ -7123,13 +7123,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8648,13 +8648,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8692,8 +8692,8 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>3</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -10181,13 +10181,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X93" s="9" t="n">
         <v>0</v>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>1</v>
@@ -10492,13 +10492,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10593,13 +10593,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10799,13 +10799,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>7</v>
@@ -11562,7 +11562,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="10" t="n">
         <v>1</v>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12039,13 +12039,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="8" t="inlineStr">
         <is>
@@ -12083,8 +12083,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12185,8 +12185,8 @@
       <c r="T112" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U112" s="9" t="n">
-        <v>0</v>
+      <c r="U112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V112" s="9" t="n">
         <v>0</v>
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13078,13 +13078,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -13177,7 +13177,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -13408,7 +13408,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -13639,7 +13639,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
